--- a/artfynd/A 59334-2025 artfynd.xlsx
+++ b/artfynd/A 59334-2025 artfynd.xlsx
@@ -1526,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130654941</v>
+        <v>130654938</v>
       </c>
       <c r="B10" t="n">
         <v>79209</v>
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440134</v>
+        <v>440117</v>
       </c>
       <c r="R10" t="n">
-        <v>7053783</v>
+        <v>7053967</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,11 +1602,6 @@
           <t>2026-01-12</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Växer på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1632,9 +1627,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130654938</v>
+        <v>130654941</v>
       </c>
       <c r="B12" t="n">
         <v>79209</v>
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440117</v>
+        <v>440134</v>
       </c>
       <c r="R12" t="n">
-        <v>7053967</v>
+        <v>7053783</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1863,6 +1863,11 @@
           <t>2026-01-12</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växer på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1888,14 +1893,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2645,7 +2645,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130654512</v>
+        <v>130654511</v>
       </c>
       <c r="B19" t="n">
         <v>57852</v>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440119</v>
+        <v>439998</v>
       </c>
       <c r="R19" t="n">
-        <v>7053934</v>
+        <v>7054180</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2747,7 +2747,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130654511</v>
+        <v>130654512</v>
       </c>
       <c r="B20" t="n">
         <v>57852</v>
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439998</v>
+        <v>440119</v>
       </c>
       <c r="R20" t="n">
-        <v>7054180</v>
+        <v>7053934</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130654931</v>
+        <v>130654933</v>
       </c>
       <c r="B22" t="n">
-        <v>57852</v>
+        <v>57849</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2962,16 +2962,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2984,7 +2984,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440195</v>
+        <v>439962</v>
       </c>
       <c r="R22" t="n">
-        <v>7053721</v>
+        <v>7053998</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>Äldre hackspår i stambasen av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130654933</v>
+        <v>130654931</v>
       </c>
       <c r="B23" t="n">
-        <v>57849</v>
+        <v>57852</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3097,16 +3097,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3119,7 +3119,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439962</v>
+        <v>440195</v>
       </c>
       <c r="R23" t="n">
-        <v>7053998</v>
+        <v>7053721</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre hackspår i stambasen av en stående död gran med full längd.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3198,12 +3198,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 59334-2025 artfynd.xlsx
+++ b/artfynd/A 59334-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,7 +804,7 @@
         <v>130654521</v>
       </c>
       <c r="B3" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130654516</v>
+        <v>130654519</v>
       </c>
       <c r="B5" t="n">
-        <v>57852</v>
+        <v>91779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,23 +1036,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1060,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440167</v>
+        <v>440188</v>
       </c>
       <c r="R5" t="n">
-        <v>7053949</v>
+        <v>7053971</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,11 +1092,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130654519</v>
+        <v>130654516</v>
       </c>
       <c r="B6" t="n">
-        <v>91778</v>
+        <v>57852</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,19 +1129,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1158,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440188</v>
+        <v>440167</v>
       </c>
       <c r="R6" t="n">
-        <v>7053971</v>
+        <v>7053949</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,6 +1189,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130654517</v>
+        <v>130654938</v>
       </c>
       <c r="B9" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,34 +1435,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ödemokojan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440178</v>
+        <v>440117</v>
       </c>
       <c r="R9" t="n">
-        <v>7053979</v>
+        <v>7053967</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,36 +1500,57 @@
           <t>2026-01-12</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130654938</v>
+        <v>130654941</v>
       </c>
       <c r="B10" t="n">
         <v>79209</v>
@@ -1564,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440117</v>
+        <v>440134</v>
       </c>
       <c r="R10" t="n">
-        <v>7053967</v>
+        <v>7053783</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,6 +1626,11 @@
           <t>2026-01-12</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växer på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1627,14 +1656,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1787,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130654941</v>
+        <v>130654517</v>
       </c>
       <c r="B12" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,37 +1822,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ödemokojan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440134</v>
+        <v>440178</v>
       </c>
       <c r="R12" t="n">
-        <v>7053783</v>
+        <v>7053979</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1886,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Växer på en gran vid en hyggeskant.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1874,39 +1895,18 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130654518</v>
+        <v>130654935</v>
       </c>
       <c r="B17" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,34 +2423,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ödemokojan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440177</v>
+        <v>439862</v>
       </c>
       <c r="R17" t="n">
-        <v>7054022</v>
+        <v>7054226</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2487,7 +2490,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,28 +2499,54 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130654935</v>
+        <v>130654518</v>
       </c>
       <c r="B18" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,37 +2554,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ödemokojan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439862</v>
+        <v>440177</v>
       </c>
       <c r="R18" t="n">
-        <v>7054226</v>
+        <v>7054022</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2592,7 +2618,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2601,44 +2627,18 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3350,6 +3350,115 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130693178</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57956</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ödemokojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>440113</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7053816</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59334-2025 artfynd.xlsx
+++ b/artfynd/A 59334-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130654937</v>
       </c>
       <c r="B2" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>130654521</v>
       </c>
       <c r="B3" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130654940</v>
       </c>
       <c r="B4" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>130654519</v>
       </c>
       <c r="B5" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>130654516</v>
       </c>
       <c r="B6" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>130654510</v>
       </c>
       <c r="B7" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>130654513</v>
       </c>
       <c r="B8" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>130654938</v>
       </c>
       <c r="B9" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>130654941</v>
       </c>
       <c r="B10" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>130654930</v>
       </c>
       <c r="B11" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>130654517</v>
       </c>
       <c r="B12" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>130654514</v>
       </c>
       <c r="B13" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>130654932</v>
       </c>
       <c r="B14" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>130654939</v>
       </c>
       <c r="B15" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>130654936</v>
       </c>
       <c r="B16" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>130654935</v>
       </c>
       <c r="B17" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>130654518</v>
       </c>
       <c r="B18" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>130654511</v>
       </c>
       <c r="B19" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>130654512</v>
       </c>
       <c r="B20" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>130654515</v>
       </c>
       <c r="B21" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>130654933</v>
       </c>
       <c r="B22" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>130654931</v>
       </c>
       <c r="B23" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>130654942</v>
       </c>
       <c r="B24" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>130693178</v>
       </c>
       <c r="B25" t="n">
-        <v>57956</v>
+        <v>57958</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 59334-2025 artfynd.xlsx
+++ b/artfynd/A 59334-2025 artfynd.xlsx
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130654519</v>
+        <v>130654516</v>
       </c>
       <c r="B5" t="n">
-        <v>91781</v>
+        <v>57854</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,19 +1036,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1056,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440188</v>
+        <v>440167</v>
       </c>
       <c r="R5" t="n">
-        <v>7053971</v>
+        <v>7053949</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,6 +1096,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130654516</v>
+        <v>130654519</v>
       </c>
       <c r="B6" t="n">
-        <v>57854</v>
+        <v>91781</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,23 +1138,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1153,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440167</v>
+        <v>440188</v>
       </c>
       <c r="R6" t="n">
-        <v>7053949</v>
+        <v>7053971</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,11 +1194,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2412,10 +2412,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130654935</v>
+        <v>130654518</v>
       </c>
       <c r="B17" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,37 +2423,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ödemokojan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>439862</v>
+        <v>440177</v>
       </c>
       <c r="R17" t="n">
-        <v>7054226</v>
+        <v>7054022</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2490,7 +2487,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2499,54 +2496,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130654518</v>
+        <v>130654935</v>
       </c>
       <c r="B18" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,34 +2525,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ödemokojan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440177</v>
+        <v>439862</v>
       </c>
       <c r="R18" t="n">
-        <v>7054022</v>
+        <v>7054226</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2618,7 +2592,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2627,18 +2601,44 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 59334-2025 artfynd.xlsx
+++ b/artfynd/A 59334-2025 artfynd.xlsx
@@ -2412,10 +2412,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130654518</v>
+        <v>130654935</v>
       </c>
       <c r="B17" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,34 +2423,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ödemokojan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440177</v>
+        <v>439862</v>
       </c>
       <c r="R17" t="n">
-        <v>7054022</v>
+        <v>7054226</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2487,7 +2490,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,28 +2499,54 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130654935</v>
+        <v>130654518</v>
       </c>
       <c r="B18" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,37 +2554,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ödemokojan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439862</v>
+        <v>440177</v>
       </c>
       <c r="R18" t="n">
-        <v>7054226</v>
+        <v>7054022</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2592,7 +2618,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2601,44 +2627,18 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 59334-2025 artfynd.xlsx
+++ b/artfynd/A 59334-2025 artfynd.xlsx
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130654938</v>
+        <v>130654930</v>
       </c>
       <c r="B9" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,26 +1435,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1462,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440117</v>
+        <v>440168</v>
       </c>
       <c r="R9" t="n">
-        <v>7053967</v>
+        <v>7053746</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,13 +1505,17 @@
           <t>2026-01-12</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), enstaka färska, några meter upp på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1527,12 +1536,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1550,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130654941</v>
+        <v>130654517</v>
       </c>
       <c r="B10" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,37 +1570,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ödemokojan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440134</v>
+        <v>440178</v>
       </c>
       <c r="R10" t="n">
-        <v>7053783</v>
+        <v>7053979</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,7 +1634,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Växer på en gran vid en hyggeskant.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1637,49 +1643,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130654930</v>
+        <v>130654938</v>
       </c>
       <c r="B11" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1687,31 +1672,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1719,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440168</v>
+        <v>440117</v>
       </c>
       <c r="R11" t="n">
-        <v>7053746</v>
+        <v>7053967</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1757,17 +1737,13 @@
           <t>2026-01-12</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), enstaka färska, några meter upp på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1788,12 +1764,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1811,10 +1787,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130654517</v>
+        <v>130654941</v>
       </c>
       <c r="B12" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,34 +1798,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ödemokojan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440178</v>
+        <v>440134</v>
       </c>
       <c r="R12" t="n">
-        <v>7053979</v>
+        <v>7053783</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1886,7 +1865,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Växer på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,18 +1874,39 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130654935</v>
+        <v>130654518</v>
       </c>
       <c r="B17" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,37 +2423,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ödemokojan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>439862</v>
+        <v>440177</v>
       </c>
       <c r="R17" t="n">
-        <v>7054226</v>
+        <v>7054022</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2490,7 +2487,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2499,54 +2496,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130654518</v>
+        <v>130654935</v>
       </c>
       <c r="B18" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,34 +2525,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ödemokojan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440177</v>
+        <v>439862</v>
       </c>
       <c r="R18" t="n">
-        <v>7054022</v>
+        <v>7054226</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2618,7 +2592,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2627,18 +2601,44 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 59334-2025 artfynd.xlsx
+++ b/artfynd/A 59334-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130654937</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>130654521</v>
       </c>
       <c r="B3" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130654940</v>
       </c>
       <c r="B4" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130654516</v>
+        <v>130654519</v>
       </c>
       <c r="B5" t="n">
-        <v>57854</v>
+        <v>91794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,23 +1036,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1060,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440167</v>
+        <v>440188</v>
       </c>
       <c r="R5" t="n">
-        <v>7053949</v>
+        <v>7053971</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,11 +1092,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130654519</v>
+        <v>130654516</v>
       </c>
       <c r="B6" t="n">
-        <v>91781</v>
+        <v>57862</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,19 +1129,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1158,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440188</v>
+        <v>440167</v>
       </c>
       <c r="R6" t="n">
-        <v>7053971</v>
+        <v>7053949</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,6 +1189,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,7 +1223,7 @@
         <v>130654510</v>
       </c>
       <c r="B7" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>130654513</v>
       </c>
       <c r="B8" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130654930</v>
+        <v>130654938</v>
       </c>
       <c r="B9" t="n">
-        <v>57854</v>
+        <v>79219</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,31 +1435,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1467,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440168</v>
+        <v>440117</v>
       </c>
       <c r="R9" t="n">
-        <v>7053746</v>
+        <v>7053967</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,17 +1500,13 @@
           <t>2026-01-12</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), enstaka färska, några meter upp på en gran vid en hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1536,12 +1527,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1559,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130654517</v>
+        <v>130654941</v>
       </c>
       <c r="B10" t="n">
-        <v>57854</v>
+        <v>79219</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,34 +1561,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ödemokojan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440178</v>
+        <v>440134</v>
       </c>
       <c r="R10" t="n">
-        <v>7053979</v>
+        <v>7053783</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,7 +1628,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Växer på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1643,28 +1637,49 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130654938</v>
+        <v>130654930</v>
       </c>
       <c r="B11" t="n">
-        <v>79211</v>
+        <v>57862</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1672,26 +1687,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1699,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440117</v>
+        <v>440168</v>
       </c>
       <c r="R11" t="n">
-        <v>7053967</v>
+        <v>7053746</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,13 +1757,17 @@
           <t>2026-01-12</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), enstaka färska, några meter upp på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1764,12 +1788,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1787,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130654941</v>
+        <v>130654517</v>
       </c>
       <c r="B12" t="n">
-        <v>79211</v>
+        <v>57862</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,37 +1822,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ödemokojan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440134</v>
+        <v>440178</v>
       </c>
       <c r="R12" t="n">
-        <v>7053783</v>
+        <v>7053979</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1886,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Växer på en gran vid en hyggeskant.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1874,39 +1895,18 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1916,7 +1916,7 @@
         <v>130654514</v>
       </c>
       <c r="B13" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>130654932</v>
       </c>
       <c r="B14" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>130654939</v>
       </c>
       <c r="B15" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>130654936</v>
       </c>
       <c r="B16" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130654518</v>
+        <v>130654935</v>
       </c>
       <c r="B17" t="n">
-        <v>57854</v>
+        <v>79219</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,34 +2423,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ödemokojan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440177</v>
+        <v>439862</v>
       </c>
       <c r="R17" t="n">
-        <v>7054022</v>
+        <v>7054226</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2487,7 +2490,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,28 +2499,54 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130654935</v>
+        <v>130654518</v>
       </c>
       <c r="B18" t="n">
-        <v>79211</v>
+        <v>57862</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,37 +2554,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ödemokojan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439862</v>
+        <v>440177</v>
       </c>
       <c r="R18" t="n">
-        <v>7054226</v>
+        <v>7054022</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2592,7 +2618,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2601,44 +2627,18 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2648,7 +2648,7 @@
         <v>130654511</v>
       </c>
       <c r="B19" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>130654512</v>
       </c>
       <c r="B20" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>130654515</v>
       </c>
       <c r="B21" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130654933</v>
+        <v>130654931</v>
       </c>
       <c r="B22" t="n">
-        <v>57851</v>
+        <v>57862</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2962,16 +2962,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2984,7 +2984,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>439962</v>
+        <v>440195</v>
       </c>
       <c r="R22" t="n">
-        <v>7053998</v>
+        <v>7053721</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Äldre hackspår i stambasen av en stående död gran med full längd.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130654931</v>
+        <v>130654933</v>
       </c>
       <c r="B23" t="n">
-        <v>57854</v>
+        <v>57859</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3097,16 +3097,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3119,7 +3119,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440195</v>
+        <v>439962</v>
       </c>
       <c r="R23" t="n">
-        <v>7053721</v>
+        <v>7053998</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>Äldre hackspår i stambasen av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3198,12 +3198,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3224,7 +3224,7 @@
         <v>130654942</v>
       </c>
       <c r="B24" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>130693178</v>
       </c>
       <c r="B25" t="n">
-        <v>57958</v>
+        <v>57966</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 59334-2025 artfynd.xlsx
+++ b/artfynd/A 59334-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130654937</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>130654521</v>
       </c>
       <c r="B3" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130654940</v>
       </c>
       <c r="B4" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>130654519</v>
       </c>
       <c r="B5" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>130654516</v>
       </c>
       <c r="B6" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>130654510</v>
       </c>
       <c r="B7" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>130654513</v>
       </c>
       <c r="B8" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>130654938</v>
       </c>
       <c r="B9" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>130654941</v>
       </c>
       <c r="B10" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>130654930</v>
       </c>
       <c r="B11" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>130654517</v>
       </c>
       <c r="B12" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>130654514</v>
       </c>
       <c r="B13" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>130654932</v>
       </c>
       <c r="B14" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>130654939</v>
       </c>
       <c r="B15" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>130654936</v>
       </c>
       <c r="B16" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>130654935</v>
       </c>
       <c r="B17" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>130654518</v>
       </c>
       <c r="B18" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>130654511</v>
       </c>
       <c r="B19" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>130654512</v>
       </c>
       <c r="B20" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>130654515</v>
       </c>
       <c r="B21" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130654931</v>
+        <v>130654933</v>
       </c>
       <c r="B22" t="n">
-        <v>57862</v>
+        <v>57860</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2962,16 +2962,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2984,7 +2984,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440195</v>
+        <v>439962</v>
       </c>
       <c r="R22" t="n">
-        <v>7053721</v>
+        <v>7053998</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
+          <t>Äldre hackspår i stambasen av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130654933</v>
+        <v>130654931</v>
       </c>
       <c r="B23" t="n">
-        <v>57859</v>
+        <v>57863</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3097,16 +3097,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3119,7 +3119,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439962</v>
+        <v>440195</v>
       </c>
       <c r="R23" t="n">
-        <v>7053998</v>
+        <v>7053721</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre hackspår i stambasen av en stående död gran med full längd.</t>
+          <t>Ringhack (savhack), färska, enstaka på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3198,12 +3198,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3224,7 +3224,7 @@
         <v>130654942</v>
       </c>
       <c r="B24" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>130693178</v>
       </c>
       <c r="B25" t="n">
-        <v>57966</v>
+        <v>57967</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 59334-2025 artfynd.xlsx
+++ b/artfynd/A 59334-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130654937</v>
       </c>
       <c r="B2" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>130654521</v>
       </c>
       <c r="B3" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130654940</v>
       </c>
       <c r="B4" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>130654519</v>
       </c>
       <c r="B5" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>130654516</v>
       </c>
       <c r="B6" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>130654510</v>
       </c>
       <c r="B7" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>130654513</v>
       </c>
       <c r="B8" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>130654938</v>
       </c>
       <c r="B9" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>130654941</v>
       </c>
       <c r="B10" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>130654930</v>
       </c>
       <c r="B11" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>130654517</v>
       </c>
       <c r="B12" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>130654514</v>
       </c>
       <c r="B13" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>130654932</v>
       </c>
       <c r="B14" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>130654939</v>
       </c>
       <c r="B15" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>130654936</v>
       </c>
       <c r="B16" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>130654935</v>
       </c>
       <c r="B17" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>130654518</v>
       </c>
       <c r="B18" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>130654511</v>
       </c>
       <c r="B19" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>130654512</v>
       </c>
       <c r="B20" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>130654515</v>
       </c>
       <c r="B21" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>130654933</v>
       </c>
       <c r="B22" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>130654931</v>
       </c>
       <c r="B23" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>130654942</v>
       </c>
       <c r="B24" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>130693178</v>
       </c>
       <c r="B25" t="n">
-        <v>57967</v>
+        <v>57968</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 59334-2025 artfynd.xlsx
+++ b/artfynd/A 59334-2025 artfynd.xlsx
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130654519</v>
+        <v>130654516</v>
       </c>
       <c r="B5" t="n">
-        <v>91796</v>
+        <v>57864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,19 +1036,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1056,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440188</v>
+        <v>440167</v>
       </c>
       <c r="R5" t="n">
-        <v>7053971</v>
+        <v>7053949</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,6 +1096,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130654516</v>
+        <v>130654519</v>
       </c>
       <c r="B6" t="n">
-        <v>57864</v>
+        <v>91796</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,23 +1138,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1153,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440167</v>
+        <v>440188</v>
       </c>
       <c r="R6" t="n">
-        <v>7053949</v>
+        <v>7053971</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,11 +1194,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2412,10 +2412,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130654935</v>
+        <v>130654518</v>
       </c>
       <c r="B17" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,37 +2423,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ödemokojan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>439862</v>
+        <v>440177</v>
       </c>
       <c r="R17" t="n">
-        <v>7054226</v>
+        <v>7054022</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2490,7 +2487,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2499,54 +2496,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130654518</v>
+        <v>130654935</v>
       </c>
       <c r="B18" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2554,34 +2525,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ödemokojan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440177</v>
+        <v>439862</v>
       </c>
       <c r="R18" t="n">
-        <v>7054022</v>
+        <v>7054226</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2618,7 +2592,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2627,18 +2601,44 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 59334-2025 artfynd.xlsx
+++ b/artfynd/A 59334-2025 artfynd.xlsx
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130654516</v>
+        <v>130654519</v>
       </c>
       <c r="B5" t="n">
-        <v>57864</v>
+        <v>91796</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,23 +1036,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1060,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440167</v>
+        <v>440188</v>
       </c>
       <c r="R5" t="n">
-        <v>7053949</v>
+        <v>7053971</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,11 +1092,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130654519</v>
+        <v>130654516</v>
       </c>
       <c r="B6" t="n">
-        <v>91796</v>
+        <v>57864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,19 +1129,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1158,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440188</v>
+        <v>440167</v>
       </c>
       <c r="R6" t="n">
-        <v>7053971</v>
+        <v>7053949</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,6 +1189,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2412,10 +2412,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130654518</v>
+        <v>130654935</v>
       </c>
       <c r="B17" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,34 +2423,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ödemokojan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440177</v>
+        <v>439862</v>
       </c>
       <c r="R17" t="n">
-        <v>7054022</v>
+        <v>7054226</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2487,7 +2490,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,28 +2499,54 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130654935</v>
+        <v>130654518</v>
       </c>
       <c r="B18" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2525,37 +2554,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ödemokojan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439862</v>
+        <v>440177</v>
       </c>
       <c r="R18" t="n">
-        <v>7054226</v>
+        <v>7054022</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2592,7 +2618,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2601,44 +2627,18 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
